--- a/excel-example/DataFromInvoice for example .xlsx
+++ b/excel-example/DataFromInvoice for example .xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="78">
   <si>
     <t>Size</t>
   </si>
@@ -230,9 +230,6 @@
   </si>
   <si>
     <t>src/main/resources/static/images/metalware/screws_with_disc_head.png</t>
-  </si>
-  <si>
-    <t>Mapped name</t>
   </si>
   <si>
     <t>Alter_rus_name</t>
@@ -249,11 +246,10 @@
 per unit</t>
   </si>
   <si>
-    <t>Alter_image_pathes</t>
-  </si>
-  <si>
-    <t>Total
-order</t>
+    <t>Original name</t>
+  </si>
+  <si>
+    <t>Alter_image_path</t>
   </si>
 </sst>
 </file>
@@ -263,7 +259,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,19 +273,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFCF8E6D"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial Narrow"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -297,7 +280,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -310,34 +293,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -359,52 +321,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -711,1074 +661,1113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:L53"/>
+  <dimension ref="A2:H51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="48.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="55.28515625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9" style="3"/>
-    <col min="10" max="11" width="9.140625" style="2"/>
-    <col min="12" max="12" width="14.7109375" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="48.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="55.28515625" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="45.75" thickBot="1">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:8" ht="45">
+      <c r="A2" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="L2" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="15.75">
-      <c r="A3" s="5">
+    </row>
+    <row r="3" spans="1:8" ht="15.75">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <v>1000</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="L3" s="14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.75">
-      <c r="A4" s="5">
+    </row>
+    <row r="4" spans="1:8" ht="15.75">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>1000</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:12" ht="15.75">
-      <c r="A5" s="9" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="15.75">
+      <c r="A5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:12" ht="15.75">
-      <c r="A6" s="5">
+      <c r="B5" s="8"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75">
+      <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>1000</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75">
-      <c r="A7" s="5">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="4" t="s">
+    <row r="7" spans="1:8" ht="15.75">
+      <c r="A7" s="4">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>1000</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75">
-      <c r="A8" s="5">
+    <row r="8" spans="1:8" ht="15.75">
+      <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="4" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>1000</v>
       </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="4" t="s">
+      <c r="G8" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75">
-      <c r="A9" s="5">
+    <row r="9" spans="1:8" ht="15.75">
+      <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="4" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>500</v>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="4" t="s">
+      <c r="G9" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75">
-      <c r="A10" s="5">
+    <row r="10" spans="1:8" ht="15.75">
+      <c r="A10" s="4">
         <v>7</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="4" t="s">
+      <c r="B10" s="4"/>
+      <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>500</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="4" t="s">
+      <c r="G10" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75">
-      <c r="A11" s="5">
+    <row r="11" spans="1:8" ht="15.75">
+      <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="4" t="s">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <v>500</v>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="4" t="s">
+      <c r="G11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:8" ht="15.75">
+      <c r="A12" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:12" ht="15.75">
-      <c r="A13" s="5">
+      <c r="B12" s="8"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75">
+      <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="4" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
         <v>250</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="4" t="s">
+      <c r="G13" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:8" ht="15.75">
+      <c r="A14" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:12" ht="15.75">
-      <c r="A15" s="5">
+      <c r="B14" s="8"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75">
+      <c r="A15" s="4">
         <v>10</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="4" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>250</v>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="4" t="s">
+      <c r="G15" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75">
-      <c r="A16" s="5">
+    <row r="16" spans="1:8" ht="15.75">
+      <c r="A16" s="4">
         <v>11</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="4" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <v>250</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="4" t="s">
+      <c r="G16" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:8" ht="15.75">
+      <c r="A17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.75">
-      <c r="A18" s="5">
+      <c r="B17" s="8"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75">
+      <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="4" t="s">
+      <c r="B18" s="4"/>
+      <c r="C18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
         <v>1000</v>
       </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="4" t="s">
+      <c r="G18" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75">
-      <c r="A19" s="5">
+    <row r="19" spans="1:8" ht="15.75">
+      <c r="A19" s="4">
         <v>13</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="4" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
         <v>1000</v>
       </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="4" t="s">
+      <c r="G19" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:8" ht="15.75">
+      <c r="A20" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" ht="15.75">
-      <c r="A21" s="5">
+      <c r="B20" s="8"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75">
+      <c r="A21" s="4">
         <v>14</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="4" t="s">
+      <c r="B21" s="4"/>
+      <c r="C21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="4">
         <v>1000</v>
       </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="4" t="s">
+      <c r="G21" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75">
-      <c r="A22" s="5">
+    <row r="22" spans="1:8" ht="15.75">
+      <c r="A22" s="4">
         <v>15</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="4" t="s">
+      <c r="B22" s="4"/>
+      <c r="C22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="4">
         <v>500</v>
       </c>
-      <c r="G22" s="8"/>
-      <c r="H22" s="4" t="s">
+      <c r="G22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75">
-      <c r="A23" s="9" t="s">
+    <row r="23" spans="1:8" ht="15.75">
+      <c r="A23" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" ht="15.75">
-      <c r="A24" s="5">
+      <c r="B23" s="8"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75">
+      <c r="A24" s="4">
         <v>16</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="4" t="s">
+      <c r="B24" s="4"/>
+      <c r="C24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="4">
         <v>1000</v>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="4" t="s">
+      <c r="G24" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.75">
-      <c r="A25" s="5">
+    <row r="25" spans="1:8" ht="15.75">
+      <c r="A25" s="4">
         <v>17</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="4" t="s">
+      <c r="B25" s="4"/>
+      <c r="C25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="4">
         <v>1000</v>
       </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="4" t="s">
+      <c r="G25" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.75">
-      <c r="A26" s="5">
+    <row r="26" spans="1:8" ht="15.75">
+      <c r="A26" s="4">
         <v>18</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="4" t="s">
+      <c r="B26" s="4"/>
+      <c r="C26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="4">
         <v>1000</v>
       </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="4" t="s">
+      <c r="G26" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.75">
-      <c r="A27" s="5">
+    <row r="27" spans="1:8" ht="15.75">
+      <c r="A27" s="4">
         <v>19</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="4" t="s">
+      <c r="B27" s="4"/>
+      <c r="C27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="4">
         <v>1000</v>
       </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="4" t="s">
+      <c r="G27" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.75">
-      <c r="A28" s="5">
+    <row r="28" spans="1:8" ht="15.75">
+      <c r="A28" s="4">
         <v>20</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="4" t="s">
+      <c r="B28" s="4"/>
+      <c r="C28" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="4">
         <v>1000</v>
       </c>
-      <c r="G28" s="8"/>
-      <c r="H28" s="4" t="s">
+      <c r="G28" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J28" s="10"/>
-    </row>
-    <row r="29" spans="1:10" ht="15.75">
-      <c r="A29" s="5">
+    </row>
+    <row r="29" spans="1:8" ht="15.75">
+      <c r="A29" s="4">
         <v>21</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="4" t="s">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="4">
         <v>500</v>
       </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="4" t="s">
+      <c r="G29" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="J29" s="10"/>
-    </row>
-    <row r="30" spans="1:10" ht="15.75">
-      <c r="A30" s="5">
+    </row>
+    <row r="30" spans="1:8" ht="15.75">
+      <c r="A30" s="4">
         <v>22</v>
       </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="4" t="s">
+      <c r="B30" s="4"/>
+      <c r="C30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="4">
         <v>1000</v>
       </c>
-      <c r="G30" s="8"/>
-      <c r="H30" s="4" t="s">
+      <c r="G30" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="J30" s="10"/>
-    </row>
-    <row r="31" spans="1:10" ht="15.75">
-      <c r="A31" s="5">
+    </row>
+    <row r="31" spans="1:8" ht="15.75">
+      <c r="A31" s="4">
         <v>23</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="4" t="s">
+      <c r="B31" s="4"/>
+      <c r="C31" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="4">
         <v>1000</v>
       </c>
-      <c r="G31" s="8"/>
-      <c r="H31" s="4" t="s">
+      <c r="G31" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" ht="15.75">
-      <c r="A32" s="5">
+    </row>
+    <row r="32" spans="1:8" ht="15.75">
+      <c r="A32" s="4">
         <v>24</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="4" t="s">
+      <c r="B32" s="4"/>
+      <c r="C32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="4">
         <v>500</v>
       </c>
-      <c r="G32" s="8"/>
-      <c r="H32" s="4" t="s">
+      <c r="G32" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.75">
-      <c r="A33" s="5">
+    <row r="33" spans="1:8" ht="15.75">
+      <c r="A33" s="4">
         <v>25</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="4" t="s">
+      <c r="B33" s="4"/>
+      <c r="C33" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="4">
         <v>500</v>
       </c>
-      <c r="G33" s="8"/>
-      <c r="H33" s="4" t="s">
+      <c r="G33" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" ht="15.75">
-      <c r="A34" s="9" t="s">
+    </row>
+    <row r="34" spans="1:8" ht="15.75">
+      <c r="A34" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="J34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" ht="15.75">
-      <c r="A35" s="5">
+      <c r="B34" s="8"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75">
+      <c r="A35" s="4">
         <v>26</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="4" t="s">
+      <c r="B35" s="4"/>
+      <c r="C35" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="4">
         <v>100</v>
       </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="4" t="s">
+      <c r="G35" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" ht="15.75">
-      <c r="A36" s="5">
+    </row>
+    <row r="36" spans="1:8" ht="15.75">
+      <c r="A36" s="4">
         <v>27</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="4" t="s">
+      <c r="B36" s="4"/>
+      <c r="C36" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="4">
         <v>100</v>
       </c>
-      <c r="G36" s="8"/>
-      <c r="H36" s="4" t="s">
+      <c r="G36" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" ht="15.75">
-      <c r="A37" s="5">
+    </row>
+    <row r="37" spans="1:8" ht="15.75">
+      <c r="A37" s="4">
         <v>28</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="4" t="s">
+      <c r="B37" s="4"/>
+      <c r="C37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="4">
         <v>100</v>
       </c>
-      <c r="G37" s="8"/>
-      <c r="H37" s="4" t="s">
+      <c r="G37" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" ht="15.75">
-      <c r="A38" s="5">
+    </row>
+    <row r="38" spans="1:8" ht="15.75">
+      <c r="A38" s="4">
         <v>29</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="4" t="s">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="4">
         <v>100</v>
       </c>
-      <c r="G38" s="8"/>
-      <c r="H38" s="4" t="s">
+      <c r="G38" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J38" s="1"/>
-    </row>
-    <row r="39" spans="1:10" ht="15.75">
-      <c r="A39" s="9" t="s">
+    </row>
+    <row r="39" spans="1:8" ht="15.75">
+      <c r="A39" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="J39" s="10"/>
-    </row>
-    <row r="40" spans="1:10" ht="15.75">
-      <c r="A40" s="5">
+      <c r="B39" s="8"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" ht="15.75">
+      <c r="A40" s="4">
         <v>30</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="4" t="s">
+      <c r="B40" s="4"/>
+      <c r="C40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="4">
         <v>80</v>
       </c>
-      <c r="G40" s="8"/>
-      <c r="H40" s="4" t="s">
+      <c r="G40" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="J40" s="10"/>
-    </row>
-    <row r="41" spans="1:10" ht="15.75">
-      <c r="A41" s="5">
+    </row>
+    <row r="41" spans="1:8" ht="15.75">
+      <c r="A41" s="4">
         <v>31</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="4" t="s">
+      <c r="B41" s="4"/>
+      <c r="C41" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="4">
         <v>60</v>
       </c>
-      <c r="G41" s="8"/>
-      <c r="H41" s="4" t="s">
+      <c r="G41" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="J41" s="10"/>
-    </row>
-    <row r="42" spans="1:10" ht="15.75">
-      <c r="A42" s="5">
+    </row>
+    <row r="42" spans="1:8" ht="15.75">
+      <c r="A42" s="4">
         <v>32</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="4" t="s">
+      <c r="B42" s="4"/>
+      <c r="C42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="4">
         <v>38</v>
       </c>
-      <c r="G42" s="8"/>
-      <c r="H42" s="4" t="s">
+      <c r="G42" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="J42" s="10"/>
-    </row>
-    <row r="43" spans="1:10" ht="15.75">
-      <c r="A43" s="5">
+    </row>
+    <row r="43" spans="1:8" ht="15.75">
+      <c r="A43" s="4">
         <v>33</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="4" t="s">
+      <c r="B43" s="4"/>
+      <c r="C43" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="4">
         <v>32</v>
       </c>
-      <c r="G43" s="8"/>
-      <c r="H43" s="4" t="s">
+      <c r="G43" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="J43" s="10"/>
-    </row>
-    <row r="44" spans="1:10" ht="15.75">
-      <c r="A44" s="5">
+    </row>
+    <row r="44" spans="1:8" ht="15.75">
+      <c r="A44" s="4">
         <v>34</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="4" t="s">
+      <c r="B44" s="4"/>
+      <c r="C44" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="4">
         <v>18</v>
       </c>
-      <c r="G44" s="8"/>
-      <c r="H44" s="4" t="s">
+      <c r="G44" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J44" s="10"/>
-    </row>
-    <row r="45" spans="1:10" ht="15.75">
-      <c r="A45" s="9" t="s">
+    </row>
+    <row r="45" spans="1:8" ht="15.75">
+      <c r="A45" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="10"/>
-    </row>
-    <row r="46" spans="1:10" ht="15.75">
-      <c r="A46" s="5">
+      <c r="B45" s="8"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8" ht="15.75">
+      <c r="A46" s="4">
         <v>35</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="4" t="s">
+      <c r="B46" s="4"/>
+      <c r="C46" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46" s="4">
         <v>80</v>
       </c>
-      <c r="G46" s="8"/>
-      <c r="H46" s="4" t="s">
+      <c r="G46" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J46" s="10"/>
-    </row>
-    <row r="47" spans="1:10" ht="15.75">
-      <c r="A47" s="5">
+    </row>
+    <row r="47" spans="1:8" ht="15.75">
+      <c r="A47" s="4">
         <v>36</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="4" t="s">
+      <c r="B47" s="4"/>
+      <c r="C47" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="4">
         <v>100</v>
       </c>
-      <c r="G47" s="8"/>
-      <c r="H47" s="4" t="s">
+      <c r="G47" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J47" s="10"/>
-    </row>
-    <row r="48" spans="1:10" ht="15.75">
-      <c r="A48" s="5">
+    </row>
+    <row r="48" spans="1:8" ht="15.75">
+      <c r="A48" s="4">
         <v>37</v>
       </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="4" t="s">
+      <c r="B48" s="4"/>
+      <c r="C48" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="4">
         <v>40</v>
       </c>
-      <c r="G48" s="8"/>
-      <c r="H48" s="4" t="s">
+      <c r="G48" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J48" s="10"/>
-    </row>
-    <row r="49" spans="1:10" ht="15.75">
-      <c r="A49" s="5">
+    </row>
+    <row r="49" spans="1:8" ht="15.75">
+      <c r="A49" s="4">
         <v>38</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="4" t="s">
+      <c r="B49" s="4"/>
+      <c r="C49" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="4">
         <v>30</v>
       </c>
-      <c r="G49" s="8"/>
-      <c r="H49" s="4" t="s">
+      <c r="G49" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J49" s="10"/>
-    </row>
-    <row r="50" spans="1:10" ht="15.75">
-      <c r="A50" s="5">
+    </row>
+    <row r="50" spans="1:8" ht="15.75">
+      <c r="A50" s="4">
         <v>39</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="4" t="s">
+      <c r="B50" s="4"/>
+      <c r="C50" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="4">
         <v>18</v>
       </c>
-      <c r="G50" s="8"/>
-      <c r="H50" s="4" t="s">
+      <c r="G50" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H50" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="J50" s="10"/>
-    </row>
-    <row r="51" spans="1:10" ht="15.75">
-      <c r="A51" s="5">
+    </row>
+    <row r="51" spans="1:8" ht="15.75">
+      <c r="A51" s="4">
         <v>40</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="4" t="s">
+      <c r="B51" s="4"/>
+      <c r="C51" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="4">
         <v>10</v>
       </c>
-      <c r="G51" s="8"/>
-      <c r="H51" s="4" t="s">
+      <c r="G51" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="J51" s="10"/>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="J52" s="10"/>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="J53" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-example/DataFromInvoice for example .xlsx
+++ b/excel-example/DataFromInvoice for example .xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="85">
   <si>
     <t>Size</t>
   </si>
@@ -250,6 +250,27 @@
   </si>
   <si>
     <t>Alter_image_path</t>
+  </si>
+  <si>
+    <t>Csk Head Pozi Drive Chipboard Screw, Partial thread, Small box packing</t>
+  </si>
+  <si>
+    <t>Pan Framing Head Self Tapping Screw, Small box packing</t>
+  </si>
+  <si>
+    <t>Pan Framing Head Self Drilling Screw, Small box packing</t>
+  </si>
+  <si>
+    <t>Self-drilling Hexagon Head Screw with collar DIN 7504-K ASD #1, with black EPDM (TK:0.5+2.0, OD:14mm), Small box packing</t>
+  </si>
+  <si>
+    <t>Self-drilling Hexagon Head Screw with collar DIN 7504-K BSD #3, with black EPDM (TK:0.5+2.0, OD:16mm), Small box packing</t>
+  </si>
+  <si>
+    <t>Cross recessed countersunk head drilling screw, BSD, with wings, Small box packing</t>
+  </si>
+  <si>
+    <t>DIN3055 Steel Wire Rope, 6x7+FC, Reel packing</t>
   </si>
 </sst>
 </file>
@@ -259,7 +280,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +298,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -321,7 +348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -356,6 +383,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -661,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H51"/>
+  <dimension ref="A2:L51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="2" bestFit="1" customWidth="1"/>
@@ -672,10 +702,12 @@
     <col min="6" max="6" width="9.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="55.28515625" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="10" width="9.140625" style="1"/>
+    <col min="11" max="12" width="33.140625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="45">
+    <row r="2" spans="1:12" ht="45">
       <c r="A2" s="9" t="s">
         <v>49</v>
       </c>
@@ -700,14 +732,19 @@
       <c r="H2" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75">
+      <c r="K2" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.75">
       <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="3" t="s">
-        <v>1</v>
+      <c r="B3" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>2</v>
@@ -721,17 +758,19 @@
       <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="K3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75">
+    <row r="4" spans="1:12" ht="15.75">
       <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
+      <c r="B4" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>6</v>
@@ -745,29 +784,30 @@
       <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="K4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75">
+    <row r="5" spans="1:12" ht="15.75">
       <c r="A5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75">
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.75">
       <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="3" t="s">
-        <v>7</v>
+      <c r="B6" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>8</v>
@@ -781,17 +821,19 @@
       <c r="G6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="K6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75">
+    <row r="7" spans="1:12" ht="15.75">
       <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="3" t="s">
-        <v>7</v>
+      <c r="B7" s="13" t="s">
+        <v>82</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>6</v>
@@ -805,17 +847,19 @@
       <c r="G7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="K7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75">
+    <row r="8" spans="1:12" ht="15.75">
       <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="3" t="s">
-        <v>7</v>
+      <c r="B8" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
@@ -829,17 +873,19 @@
       <c r="G8" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="K8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75">
+    <row r="9" spans="1:12" ht="15.75">
       <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="3" t="s">
-        <v>7</v>
+      <c r="B9" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
@@ -853,17 +899,19 @@
       <c r="G9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="K9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75">
+    <row r="10" spans="1:12" ht="15.75">
       <c r="A10" s="4">
         <v>7</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="3" t="s">
-        <v>7</v>
+      <c r="B10" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>11</v>
@@ -877,17 +925,19 @@
       <c r="G10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="K10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75">
+    <row r="11" spans="1:12" ht="15.75">
       <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
-        <v>7</v>
+      <c r="B11" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>12</v>
@@ -901,29 +951,31 @@
       <c r="G11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="K11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75">
+    <row r="12" spans="1:12" ht="15.75">
       <c r="A12" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="3"/>
+      <c r="B12" s="13"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75">
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.75">
       <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="3" t="s">
-        <v>7</v>
+      <c r="B13" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>13</v>
@@ -937,29 +989,31 @@
       <c r="G13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="K13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75">
+    <row r="14" spans="1:12" ht="15.75">
       <c r="A14" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="3"/>
+      <c r="B14" s="13"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75">
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" ht="15.75">
       <c r="A15" s="4">
         <v>10</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="3" t="s">
-        <v>7</v>
+      <c r="B15" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>14</v>
@@ -973,17 +1027,19 @@
       <c r="G15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="K15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75">
+    <row r="16" spans="1:12" ht="15.75">
       <c r="A16" s="4">
         <v>11</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="3" t="s">
-        <v>7</v>
+      <c r="B16" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>15</v>
@@ -997,29 +1053,31 @@
       <c r="G16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="K16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75">
+    <row r="17" spans="1:12" ht="15.75">
       <c r="A17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="3"/>
+      <c r="B17" s="13"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75">
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.75">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="3" t="s">
-        <v>16</v>
+      <c r="B18" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>17</v>
@@ -1033,17 +1091,19 @@
       <c r="G18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="K18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75">
+    <row r="19" spans="1:12" ht="15.75">
       <c r="A19" s="4">
         <v>13</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="3" t="s">
-        <v>16</v>
+      <c r="B19" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>19</v>
@@ -1057,29 +1117,31 @@
       <c r="G19" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="K19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75">
+    <row r="20" spans="1:12" ht="15.75">
       <c r="A20" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="3"/>
+      <c r="B20" s="13"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="7"/>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75">
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="1:12" ht="15.75">
       <c r="A21" s="4">
         <v>14</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="3" t="s">
-        <v>20</v>
+      <c r="B21" s="13" t="s">
+        <v>82</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>21</v>
@@ -1093,17 +1155,19 @@
       <c r="G21" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="K21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75">
+    <row r="22" spans="1:12" ht="15.75">
       <c r="A22" s="4">
         <v>15</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="3" t="s">
-        <v>20</v>
+      <c r="B22" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>23</v>
@@ -1117,29 +1181,31 @@
       <c r="G22" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="K22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75">
+    <row r="23" spans="1:12" ht="15.75">
       <c r="A23" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="3"/>
+      <c r="B23" s="13"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75">
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.75">
       <c r="A24" s="4">
         <v>16</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="3" t="s">
-        <v>24</v>
+      <c r="B24" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>25</v>
@@ -1153,18 +1219,18 @@
       <c r="G24" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="K24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75">
+    <row r="25" spans="1:12" ht="15.75">
       <c r="A25" s="4">
         <v>17</v>
       </c>
       <c r="B25" s="4"/>
-      <c r="C25" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D25" s="5" t="s">
         <v>26</v>
       </c>
@@ -1177,18 +1243,18 @@
       <c r="G25" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="K25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15.75">
+    <row r="26" spans="1:12" ht="15.75">
       <c r="A26" s="4">
         <v>18</v>
       </c>
       <c r="B26" s="4"/>
-      <c r="C26" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D26" s="5" t="s">
         <v>27</v>
       </c>
@@ -1201,18 +1267,18 @@
       <c r="G26" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="K26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75">
+    <row r="27" spans="1:12" ht="15.75">
       <c r="A27" s="4">
         <v>19</v>
       </c>
       <c r="B27" s="4"/>
-      <c r="C27" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D27" s="5" t="s">
         <v>28</v>
       </c>
@@ -1225,18 +1291,18 @@
       <c r="G27" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75">
+    <row r="28" spans="1:12" ht="15.75">
       <c r="A28" s="4">
         <v>20</v>
       </c>
       <c r="B28" s="4"/>
-      <c r="C28" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D28" s="5" t="s">
         <v>29</v>
       </c>
@@ -1249,18 +1315,18 @@
       <c r="G28" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="K28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75">
+    <row r="29" spans="1:12" ht="15.75">
       <c r="A29" s="4">
         <v>21</v>
       </c>
       <c r="B29" s="4"/>
-      <c r="C29" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D29" s="5" t="s">
         <v>30</v>
       </c>
@@ -1273,18 +1339,18 @@
       <c r="G29" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="K29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75">
+    <row r="30" spans="1:12" ht="15.75">
       <c r="A30" s="4">
         <v>22</v>
       </c>
       <c r="B30" s="4"/>
-      <c r="C30" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D30" s="5" t="s">
         <v>31</v>
       </c>
@@ -1297,18 +1363,18 @@
       <c r="G30" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="K30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75">
+    <row r="31" spans="1:12" ht="15.75">
       <c r="A31" s="4">
         <v>23</v>
       </c>
       <c r="B31" s="4"/>
-      <c r="C31" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D31" s="5" t="s">
         <v>32</v>
       </c>
@@ -1321,18 +1387,18 @@
       <c r="G31" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="K31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75">
+    <row r="32" spans="1:12" ht="15.75">
       <c r="A32" s="4">
         <v>24</v>
       </c>
       <c r="B32" s="4"/>
-      <c r="C32" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D32" s="5" t="s">
         <v>33</v>
       </c>
@@ -1345,18 +1411,18 @@
       <c r="G32" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="K32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75">
+    <row r="33" spans="1:12" ht="15.75">
       <c r="A33" s="4">
         <v>25</v>
       </c>
       <c r="B33" s="4"/>
-      <c r="C33" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D33" s="5" t="s">
         <v>34</v>
       </c>
@@ -1369,30 +1435,30 @@
       <c r="G33" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="K33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75">
+    <row r="34" spans="1:12" ht="15.75">
       <c r="A34" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B34" s="8"/>
-      <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="7"/>
-      <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75">
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="1:12" ht="15.75">
       <c r="A35" s="4">
         <v>26</v>
       </c>
       <c r="B35" s="4"/>
-      <c r="C35" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D35" s="5" t="s">
         <v>36</v>
       </c>
@@ -1405,18 +1471,18 @@
       <c r="G35" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="K35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75">
+    <row r="36" spans="1:12" ht="15.75">
       <c r="A36" s="4">
         <v>27</v>
       </c>
       <c r="B36" s="4"/>
-      <c r="C36" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D36" s="5" t="s">
         <v>37</v>
       </c>
@@ -1429,18 +1495,18 @@
       <c r="G36" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="K36" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75">
+    <row r="37" spans="1:12" ht="15.75">
       <c r="A37" s="4">
         <v>28</v>
       </c>
       <c r="B37" s="4"/>
-      <c r="C37" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D37" s="5" t="s">
         <v>38</v>
       </c>
@@ -1453,18 +1519,18 @@
       <c r="G37" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="K37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75">
+    <row r="38" spans="1:12" ht="15.75">
       <c r="A38" s="4">
         <v>29</v>
       </c>
       <c r="B38" s="4"/>
-      <c r="C38" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D38" s="5" t="s">
         <v>39</v>
       </c>
@@ -1477,30 +1543,30 @@
       <c r="G38" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="K38" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L38" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15.75">
+    <row r="39" spans="1:12" ht="15.75">
       <c r="A39" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B39" s="8"/>
-      <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="7"/>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" ht="15.75">
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="1:12" ht="15.75">
       <c r="A40" s="4">
         <v>30</v>
       </c>
       <c r="B40" s="4"/>
-      <c r="C40" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="D40" s="5" t="s">
         <v>41</v>
       </c>
@@ -1513,18 +1579,18 @@
       <c r="G40" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="K40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L40" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.75">
+    <row r="41" spans="1:12" ht="15.75">
       <c r="A41" s="4">
         <v>31</v>
       </c>
       <c r="B41" s="4"/>
-      <c r="C41" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="D41" s="5" t="s">
         <v>42</v>
       </c>
@@ -1537,18 +1603,18 @@
       <c r="G41" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="K41" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75">
+    <row r="42" spans="1:12" ht="15.75">
       <c r="A42" s="4">
         <v>32</v>
       </c>
       <c r="B42" s="4"/>
-      <c r="C42" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="D42" s="5" t="s">
         <v>43</v>
       </c>
@@ -1561,18 +1627,18 @@
       <c r="G42" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="K42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75">
+    <row r="43" spans="1:12" ht="15.75">
       <c r="A43" s="4">
         <v>33</v>
       </c>
       <c r="B43" s="4"/>
-      <c r="C43" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="D43" s="5" t="s">
         <v>44</v>
       </c>
@@ -1585,18 +1651,18 @@
       <c r="G43" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="K43" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L43" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75">
+    <row r="44" spans="1:12" ht="15.75">
       <c r="A44" s="4">
         <v>34</v>
       </c>
       <c r="B44" s="4"/>
-      <c r="C44" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="D44" s="5" t="s">
         <v>45</v>
       </c>
@@ -1609,30 +1675,30 @@
       <c r="G44" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="K44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75">
+    <row r="45" spans="1:12" ht="15.75">
       <c r="A45" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B45" s="8"/>
-      <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="7"/>
-      <c r="H45" s="3"/>
-    </row>
-    <row r="46" spans="1:8" ht="15.75">
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75">
       <c r="A46" s="4">
         <v>35</v>
       </c>
       <c r="B46" s="4"/>
-      <c r="C46" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D46" s="5" t="s">
         <v>41</v>
       </c>
@@ -1645,18 +1711,18 @@
       <c r="G46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="K46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75">
+    <row r="47" spans="1:12" ht="15.75">
       <c r="A47" s="4">
         <v>36</v>
       </c>
       <c r="B47" s="4"/>
-      <c r="C47" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D47" s="5" t="s">
         <v>42</v>
       </c>
@@ -1669,18 +1735,18 @@
       <c r="G47" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="K47" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.75">
+    <row r="48" spans="1:12" ht="15.75">
       <c r="A48" s="4">
         <v>37</v>
       </c>
       <c r="B48" s="4"/>
-      <c r="C48" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D48" s="5" t="s">
         <v>43</v>
       </c>
@@ -1693,18 +1759,18 @@
       <c r="G48" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="K48" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75">
+    <row r="49" spans="1:12" ht="15.75">
       <c r="A49" s="4">
         <v>38</v>
       </c>
       <c r="B49" s="4"/>
-      <c r="C49" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D49" s="5" t="s">
         <v>44</v>
       </c>
@@ -1717,18 +1783,18 @@
       <c r="G49" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="K49" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L49" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75">
+    <row r="50" spans="1:12" ht="15.75">
       <c r="A50" s="4">
         <v>39</v>
       </c>
       <c r="B50" s="4"/>
-      <c r="C50" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D50" s="5" t="s">
         <v>45</v>
       </c>
@@ -1741,18 +1807,18 @@
       <c r="G50" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="K50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.75">
+    <row r="51" spans="1:12" ht="15.75">
       <c r="A51" s="4">
         <v>40</v>
       </c>
       <c r="B51" s="4"/>
-      <c r="C51" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D51" s="5" t="s">
         <v>47</v>
       </c>
@@ -1765,7 +1831,10 @@
       <c r="G51" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="K51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L51" s="3" t="s">
         <v>68</v>
       </c>
     </row>

--- a/excel-example/DataFromInvoice for example .xlsx
+++ b/excel-example/DataFromInvoice for example .xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="85">
   <si>
     <t>Size</t>
   </si>
@@ -702,7 +702,8 @@
     <col min="6" max="6" width="9.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="55.28515625" style="2" customWidth="1"/>
-    <col min="9" max="10" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="16.5703125" style="1" customWidth="1"/>
     <col min="11" max="12" width="33.140625" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -732,6 +733,9 @@
       <c r="H2" s="10" t="s">
         <v>77</v>
       </c>
+      <c r="J2" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="K2" s="10" t="s">
         <v>72</v>
       </c>
@@ -746,6 +750,9 @@
       <c r="B3" s="13" t="s">
         <v>78</v>
       </c>
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
@@ -757,6 +764,12 @@
       </c>
       <c r="G3" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>1</v>
@@ -772,6 +785,9 @@
       <c r="B4" s="13" t="s">
         <v>79</v>
       </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
@@ -783,6 +799,12 @@
       </c>
       <c r="G4" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>5</v>
@@ -795,10 +817,13 @@
       <c r="A5" s="8" t="s">
         <v>48</v>
       </c>
+      <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="7"/>
+      <c r="H5" s="3"/>
+      <c r="J5" s="2"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
@@ -809,6 +834,9 @@
       <c r="B6" s="13" t="s">
         <v>81</v>
       </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
@@ -821,6 +849,12 @@
       <c r="G6" s="7" t="s">
         <v>4</v>
       </c>
+      <c r="H6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>81</v>
+      </c>
       <c r="K6" s="3" t="s">
         <v>7</v>
       </c>
@@ -835,6 +869,9 @@
       <c r="B7" s="13" t="s">
         <v>82</v>
       </c>
+      <c r="C7" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="D7" s="5" t="s">
         <v>6</v>
       </c>
@@ -846,6 +883,12 @@
       </c>
       <c r="G7" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>82</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>7</v>
@@ -861,6 +904,9 @@
       <c r="B8" s="13" t="s">
         <v>83</v>
       </c>
+      <c r="C8" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
@@ -872,6 +918,12 @@
       </c>
       <c r="G8" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>7</v>
@@ -887,6 +939,9 @@
       <c r="B9" s="13" t="s">
         <v>84</v>
       </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="D9" s="5" t="s">
         <v>10</v>
       </c>
@@ -898,6 +953,12 @@
       </c>
       <c r="G9" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>7</v>
@@ -913,6 +974,9 @@
       <c r="B10" s="13" t="s">
         <v>78</v>
       </c>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="D10" s="5" t="s">
         <v>11</v>
       </c>
@@ -924,6 +988,12 @@
       </c>
       <c r="G10" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>7</v>
@@ -939,6 +1009,9 @@
       <c r="B11" s="13" t="s">
         <v>79</v>
       </c>
+      <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="D11" s="5" t="s">
         <v>12</v>
       </c>
@@ -950,6 +1023,12 @@
       </c>
       <c r="G11" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>7</v>
@@ -963,10 +1042,13 @@
         <v>48</v>
       </c>
       <c r="B12" s="13"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="7"/>
+      <c r="H12" s="3"/>
+      <c r="J12" s="13"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
     </row>
@@ -977,6 +1059,9 @@
       <c r="B13" s="13" t="s">
         <v>81</v>
       </c>
+      <c r="C13" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="D13" s="5" t="s">
         <v>13</v>
       </c>
@@ -988,6 +1073,12 @@
       </c>
       <c r="G13" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>7</v>
@@ -1001,10 +1092,13 @@
         <v>48</v>
       </c>
       <c r="B14" s="13"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="7"/>
+      <c r="H14" s="3"/>
+      <c r="J14" s="13"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
@@ -1015,6 +1109,9 @@
       <c r="B15" s="13" t="s">
         <v>83</v>
       </c>
+      <c r="C15" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="D15" s="5" t="s">
         <v>14</v>
       </c>
@@ -1026,6 +1123,12 @@
       </c>
       <c r="G15" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>7</v>
@@ -1041,6 +1144,9 @@
       <c r="B16" s="13" t="s">
         <v>84</v>
       </c>
+      <c r="C16" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="D16" s="5" t="s">
         <v>15</v>
       </c>
@@ -1052,6 +1158,12 @@
       </c>
       <c r="G16" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>7</v>
@@ -1065,10 +1177,13 @@
         <v>48</v>
       </c>
       <c r="B17" s="13"/>
+      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="7"/>
+      <c r="H17" s="3"/>
+      <c r="J17" s="13"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
@@ -1079,6 +1194,9 @@
       <c r="B18" s="13" t="s">
         <v>79</v>
       </c>
+      <c r="C18" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D18" s="5" t="s">
         <v>17</v>
       </c>
@@ -1090,6 +1208,12 @@
       </c>
       <c r="G18" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>16</v>
@@ -1105,6 +1229,9 @@
       <c r="B19" s="13" t="s">
         <v>80</v>
       </c>
+      <c r="C19" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D19" s="5" t="s">
         <v>19</v>
       </c>
@@ -1116,6 +1243,12 @@
       </c>
       <c r="G19" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>16</v>
@@ -1129,10 +1262,13 @@
         <v>48</v>
       </c>
       <c r="B20" s="13"/>
+      <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="7"/>
+      <c r="H20" s="3"/>
+      <c r="J20" s="13"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
@@ -1143,6 +1279,9 @@
       <c r="B21" s="13" t="s">
         <v>82</v>
       </c>
+      <c r="C21" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="D21" s="5" t="s">
         <v>21</v>
       </c>
@@ -1154,6 +1293,12 @@
       </c>
       <c r="G21" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>82</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>20</v>
@@ -1169,6 +1314,9 @@
       <c r="B22" s="13" t="s">
         <v>83</v>
       </c>
+      <c r="C22" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="D22" s="5" t="s">
         <v>23</v>
       </c>
@@ -1180,6 +1328,12 @@
       </c>
       <c r="G22" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>20</v>
@@ -1193,10 +1347,13 @@
         <v>48</v>
       </c>
       <c r="B23" s="13"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="7"/>
+      <c r="H23" s="3"/>
+      <c r="J23" s="13"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
     </row>
@@ -1207,6 +1364,9 @@
       <c r="B24" s="13" t="s">
         <v>80</v>
       </c>
+      <c r="C24" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
@@ -1218,6 +1378,12 @@
       </c>
       <c r="G24" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>24</v>
@@ -1231,6 +1397,9 @@
         <v>17</v>
       </c>
       <c r="B25" s="4"/>
+      <c r="C25" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="D25" s="5" t="s">
         <v>26</v>
       </c>
@@ -1255,6 +1424,9 @@
         <v>18</v>
       </c>
       <c r="B26" s="4"/>
+      <c r="C26" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="D26" s="5" t="s">
         <v>27</v>
       </c>
@@ -1279,6 +1451,9 @@
         <v>19</v>
       </c>
       <c r="B27" s="4"/>
+      <c r="C27" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="D27" s="5" t="s">
         <v>28</v>
       </c>
@@ -1303,6 +1478,9 @@
         <v>20</v>
       </c>
       <c r="B28" s="4"/>
+      <c r="C28" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="D28" s="5" t="s">
         <v>29</v>
       </c>
@@ -1327,6 +1505,9 @@
         <v>21</v>
       </c>
       <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="D29" s="5" t="s">
         <v>30</v>
       </c>
@@ -1351,6 +1532,9 @@
         <v>22</v>
       </c>
       <c r="B30" s="4"/>
+      <c r="C30" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="D30" s="5" t="s">
         <v>31</v>
       </c>
@@ -1375,6 +1559,9 @@
         <v>23</v>
       </c>
       <c r="B31" s="4"/>
+      <c r="C31" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="D31" s="5" t="s">
         <v>32</v>
       </c>
@@ -1399,6 +1586,9 @@
         <v>24</v>
       </c>
       <c r="B32" s="4"/>
+      <c r="C32" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="D32" s="5" t="s">
         <v>33</v>
       </c>
@@ -1423,6 +1613,9 @@
         <v>25</v>
       </c>
       <c r="B33" s="4"/>
+      <c r="C33" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="D33" s="5" t="s">
         <v>34</v>
       </c>
@@ -1459,6 +1652,9 @@
         <v>26</v>
       </c>
       <c r="B35" s="4"/>
+      <c r="C35" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="D35" s="5" t="s">
         <v>36</v>
       </c>
@@ -1483,6 +1679,9 @@
         <v>27</v>
       </c>
       <c r="B36" s="4"/>
+      <c r="C36" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="D36" s="5" t="s">
         <v>37</v>
       </c>
@@ -1507,6 +1706,9 @@
         <v>28</v>
       </c>
       <c r="B37" s="4"/>
+      <c r="C37" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="D37" s="5" t="s">
         <v>38</v>
       </c>
@@ -1531,6 +1733,9 @@
         <v>29</v>
       </c>
       <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="D38" s="5" t="s">
         <v>39</v>
       </c>
@@ -1567,6 +1772,9 @@
         <v>30</v>
       </c>
       <c r="B40" s="4"/>
+      <c r="C40" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="D40" s="5" t="s">
         <v>41</v>
       </c>
@@ -1579,6 +1787,7 @@
       <c r="G40" s="7" t="s">
         <v>4</v>
       </c>
+      <c r="H40" s="3"/>
       <c r="K40" s="3" t="s">
         <v>40</v>
       </c>
@@ -1591,6 +1800,9 @@
         <v>31</v>
       </c>
       <c r="B41" s="4"/>
+      <c r="C41" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="D41" s="5" t="s">
         <v>42</v>
       </c>
@@ -1603,6 +1815,7 @@
       <c r="G41" s="7" t="s">
         <v>4</v>
       </c>
+      <c r="H41" s="3"/>
       <c r="K41" s="3" t="s">
         <v>40</v>
       </c>
@@ -1615,6 +1828,9 @@
         <v>32</v>
       </c>
       <c r="B42" s="4"/>
+      <c r="C42" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="D42" s="5" t="s">
         <v>43</v>
       </c>
@@ -1627,6 +1843,7 @@
       <c r="G42" s="7" t="s">
         <v>4</v>
       </c>
+      <c r="H42" s="3"/>
       <c r="K42" s="3" t="s">
         <v>40</v>
       </c>
@@ -1639,6 +1856,9 @@
         <v>33</v>
       </c>
       <c r="B43" s="4"/>
+      <c r="C43" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="D43" s="5" t="s">
         <v>44</v>
       </c>
@@ -1651,6 +1871,7 @@
       <c r="G43" s="7" t="s">
         <v>4</v>
       </c>
+      <c r="H43" s="3"/>
       <c r="K43" s="3" t="s">
         <v>40</v>
       </c>
@@ -1663,6 +1884,9 @@
         <v>34</v>
       </c>
       <c r="B44" s="4"/>
+      <c r="C44" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="D44" s="5" t="s">
         <v>45</v>
       </c>
@@ -1675,6 +1899,7 @@
       <c r="G44" s="7" t="s">
         <v>4</v>
       </c>
+      <c r="H44" s="3"/>
       <c r="K44" s="3" t="s">
         <v>40</v>
       </c>
@@ -1699,6 +1924,9 @@
         <v>35</v>
       </c>
       <c r="B46" s="4"/>
+      <c r="C46" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="D46" s="5" t="s">
         <v>41</v>
       </c>
@@ -1710,6 +1938,9 @@
       </c>
       <c r="G46" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>46</v>
@@ -1723,6 +1954,9 @@
         <v>36</v>
       </c>
       <c r="B47" s="4"/>
+      <c r="C47" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="D47" s="5" t="s">
         <v>42</v>
       </c>
@@ -1734,6 +1968,9 @@
       </c>
       <c r="G47" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>46</v>
@@ -1747,6 +1984,9 @@
         <v>37</v>
       </c>
       <c r="B48" s="4"/>
+      <c r="C48" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="D48" s="5" t="s">
         <v>43</v>
       </c>
@@ -1758,6 +1998,9 @@
       </c>
       <c r="G48" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>46</v>
@@ -1771,6 +2014,9 @@
         <v>38</v>
       </c>
       <c r="B49" s="4"/>
+      <c r="C49" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="D49" s="5" t="s">
         <v>44</v>
       </c>
@@ -1782,6 +2028,9 @@
       </c>
       <c r="G49" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>46</v>
@@ -1795,6 +2044,9 @@
         <v>39</v>
       </c>
       <c r="B50" s="4"/>
+      <c r="C50" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="D50" s="5" t="s">
         <v>45</v>
       </c>
@@ -1806,6 +2058,9 @@
       </c>
       <c r="G50" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>46</v>
@@ -1819,6 +2074,9 @@
         <v>40</v>
       </c>
       <c r="B51" s="4"/>
+      <c r="C51" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="D51" s="5" t="s">
         <v>47</v>
       </c>
@@ -1830,6 +2088,9 @@
       </c>
       <c r="G51" s="7" t="s">
         <v>4</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>46</v>
